--- a/artfynd/A 50360-2025 artfynd.xlsx
+++ b/artfynd/A 50360-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133964901</v>
+        <v>133965792</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>30 maj 26, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590364</v>
+        <v>590396</v>
       </c>
       <c r="R2" t="n">
-        <v>7097857</v>
+        <v>7098248</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133964875</v>
+        <v>133964901</v>
       </c>
       <c r="B3" t="n">
         <v>79359</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590484</v>
+        <v>590364</v>
       </c>
       <c r="R3" t="n">
-        <v>7098087</v>
+        <v>7097857</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133964893</v>
+        <v>133964875</v>
       </c>
       <c r="B5" t="n">
-        <v>91980</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,19 +1019,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590383</v>
+        <v>590484</v>
       </c>
       <c r="R5" t="n">
-        <v>7097909</v>
+        <v>7098087</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1088,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133965792</v>
+        <v>133964893</v>
       </c>
       <c r="B6" t="n">
-        <v>80474</v>
+        <v>91980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,37 +1130,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>30 maj 26, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590396</v>
+        <v>590383</v>
       </c>
       <c r="R6" t="n">
-        <v>7098248</v>
+        <v>7097909</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,12 +1210,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1675,45 +1675,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133964967</v>
+        <v>133965724</v>
       </c>
       <c r="B11" t="n">
-        <v>91960</v>
+        <v>99203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Åsele lördag invent., Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590510</v>
+        <v>590654</v>
       </c>
       <c r="R11" t="n">
-        <v>7098266</v>
+        <v>7098070</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,12 +1770,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj, Christoffer Boman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1786,45 +1786,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133965724</v>
+        <v>133964967</v>
       </c>
       <c r="B12" t="n">
-        <v>99203</v>
+        <v>91960</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åsele lördag invent., Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590654</v>
+        <v>590510</v>
       </c>
       <c r="R12" t="n">
-        <v>7098070</v>
+        <v>7098266</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,12 +1881,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Katerina Shytaj, Christoffer Boman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133964243</v>
+        <v>133964951</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>83349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,37 +2241,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blåkullbäcken, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590710</v>
+        <v>590464</v>
       </c>
       <c r="R16" t="n">
-        <v>7098212</v>
+        <v>7098263</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,12 +2310,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Pa granlåga</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2330,12 +2325,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2458,32 +2453,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133964854</v>
+        <v>133964835</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>99203</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2493,10 +2488,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590630</v>
+        <v>590706</v>
       </c>
       <c r="R18" t="n">
-        <v>7098063</v>
+        <v>7098095</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2528,7 +2523,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2538,12 +2533,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,7 +2553,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2574,32 +2564,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133964835</v>
+        <v>133964854</v>
       </c>
       <c r="B19" t="n">
-        <v>99203</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2609,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590706</v>
+        <v>590630</v>
       </c>
       <c r="R19" t="n">
-        <v>7098095</v>
+        <v>7098063</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2644,7 +2634,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2654,7 +2644,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2674,7 +2669,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2685,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133964951</v>
+        <v>133964243</v>
       </c>
       <c r="B20" t="n">
-        <v>83349</v>
+        <v>79359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2696,37 +2691,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Blåkullbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590464</v>
+        <v>590710</v>
       </c>
       <c r="R20" t="n">
-        <v>7098263</v>
+        <v>7098212</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2755,7 +2750,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2765,7 +2760,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Pa granlåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,12 +2780,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2796,10 +2796,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133964865</v>
+        <v>133965791</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,37 +2807,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>30 maj 26, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590567</v>
+        <v>590412</v>
       </c>
       <c r="R21" t="n">
-        <v>7098043</v>
+        <v>7098210</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,12 +2891,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3018,10 +3018,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133964898</v>
+        <v>133964865</v>
       </c>
       <c r="B23" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,21 +3029,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590367</v>
+        <v>590567</v>
       </c>
       <c r="R23" t="n">
-        <v>7097883</v>
+        <v>7098043</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3129,10 +3129,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133964882</v>
+        <v>133964898</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,21 +3140,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590358</v>
+        <v>590367</v>
       </c>
       <c r="R24" t="n">
-        <v>7098027</v>
+        <v>7097883</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133965791</v>
+        <v>133964882</v>
       </c>
       <c r="B25" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3251,37 +3251,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>30 maj 26, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590412</v>
+        <v>590358</v>
       </c>
       <c r="R25" t="n">
-        <v>7098210</v>
+        <v>7098027</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,12 +3335,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3690,32 +3690,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133964829</v>
+        <v>133964833</v>
       </c>
       <c r="B29" t="n">
-        <v>99203</v>
+        <v>79359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>590712</v>
+        <v>590703</v>
       </c>
       <c r="R29" t="n">
-        <v>7098203</v>
+        <v>7098166</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,32 +3912,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133964833</v>
+        <v>133964829</v>
       </c>
       <c r="B31" t="n">
-        <v>79359</v>
+        <v>99203</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590703</v>
+        <v>590712</v>
       </c>
       <c r="R31" t="n">
-        <v>7098166</v>
+        <v>7098203</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4356,10 +4356,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133964245</v>
+        <v>133964956</v>
       </c>
       <c r="B35" t="n">
-        <v>80474</v>
+        <v>91956</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4367,37 +4367,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Blåkullbäcken, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>590419</v>
+        <v>590502</v>
       </c>
       <c r="R35" t="n">
-        <v>7098217</v>
+        <v>7098260</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4436,12 +4436,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4456,12 +4451,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4472,10 +4467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133964956</v>
+        <v>133964245</v>
       </c>
       <c r="B36" t="n">
-        <v>91956</v>
+        <v>80474</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4483,37 +4478,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Blåkullbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>590502</v>
+        <v>590419</v>
       </c>
       <c r="R36" t="n">
-        <v>7098260</v>
+        <v>7098217</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4542,7 +4537,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4552,7 +4547,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4567,12 +4567,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4805,7 +4805,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133964915</v>
+        <v>133964880</v>
       </c>
       <c r="B39" t="n">
         <v>96399</v>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>590241</v>
+        <v>590370</v>
       </c>
       <c r="R39" t="n">
-        <v>7097878</v>
+        <v>7098043</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4916,7 +4916,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133964880</v>
+        <v>133964915</v>
       </c>
       <c r="B40" t="n">
         <v>96399</v>
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>590370</v>
+        <v>590241</v>
       </c>
       <c r="R40" t="n">
-        <v>7098043</v>
+        <v>7097878</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5027,45 +5027,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133965723</v>
+        <v>133964927</v>
       </c>
       <c r="B41" t="n">
-        <v>99203</v>
+        <v>80474</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Åsele lördag invent., Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>590706</v>
+        <v>590366</v>
       </c>
       <c r="R41" t="n">
-        <v>7098126</v>
+        <v>7097993</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5122,12 +5122,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Katerina Shytaj, Christoffer Boman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5138,10 +5138,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133965725</v>
+        <v>133964858</v>
       </c>
       <c r="B42" t="n">
-        <v>80478</v>
+        <v>96399</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5149,37 +5149,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6461</v>
+        <v>2809</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Åsele lördag invent., Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>590626</v>
+        <v>590638</v>
       </c>
       <c r="R42" t="n">
-        <v>7098051</v>
+        <v>7098054</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5233,12 +5233,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Katerina Shytaj, Christoffer Boman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5360,10 +5360,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133964858</v>
+        <v>133964929</v>
       </c>
       <c r="B44" t="n">
-        <v>96399</v>
+        <v>80424</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5371,21 +5371,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2809</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5395,13 +5395,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>590638</v>
+        <v>590366</v>
       </c>
       <c r="R44" t="n">
-        <v>7098054</v>
+        <v>7097993</v>
       </c>
       <c r="S44" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,45 +5471,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133964869</v>
+        <v>133965725</v>
       </c>
       <c r="B45" t="n">
-        <v>83208</v>
+        <v>80478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Åsele lördag invent., Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>590555</v>
+        <v>590626</v>
       </c>
       <c r="R45" t="n">
-        <v>7098084</v>
+        <v>7098051</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5560,19 +5560,18 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj, Christoffer Boman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5583,10 +5582,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133964927</v>
+        <v>133964869</v>
       </c>
       <c r="B46" t="n">
-        <v>80474</v>
+        <v>83208</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5594,21 +5593,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5618,10 +5617,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>590366</v>
+        <v>590555</v>
       </c>
       <c r="R46" t="n">
-        <v>7097993</v>
+        <v>7098084</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5653,7 +5652,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5663,7 +5662,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5672,6 +5671,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5694,10 +5694,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133964929</v>
+        <v>133965723</v>
       </c>
       <c r="B47" t="n">
-        <v>80424</v>
+        <v>99203</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5705,34 +5705,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Åsele lördag invent., Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>590366</v>
+        <v>590706</v>
       </c>
       <c r="R47" t="n">
-        <v>7097993</v>
+        <v>7098126</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5789,12 +5789,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj, Christoffer Boman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5925,34 +5925,30 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133964930</v>
+        <v>133964877</v>
       </c>
       <c r="B49" t="n">
-        <v>99203</v>
+        <v>91980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5960,10 +5956,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>590389</v>
+        <v>590454</v>
       </c>
       <c r="R49" t="n">
-        <v>7098071</v>
+        <v>7098077</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5995,7 +5991,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6005,7 +6001,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6036,10 +6032,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133964871</v>
+        <v>133964836</v>
       </c>
       <c r="B50" t="n">
-        <v>57972</v>
+        <v>91956</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6047,21 +6043,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6071,10 +6067,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>590527</v>
+        <v>590719</v>
       </c>
       <c r="R50" t="n">
-        <v>7098091</v>
+        <v>7098092</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6106,7 +6102,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6116,12 +6112,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:04</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6141,7 +6132,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6152,32 +6143,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133964961</v>
+        <v>133964930</v>
       </c>
       <c r="B51" t="n">
-        <v>91956</v>
+        <v>99203</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6187,10 +6178,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>590507</v>
+        <v>590389</v>
       </c>
       <c r="R51" t="n">
-        <v>7098331</v>
+        <v>7098071</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6222,7 +6213,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6232,7 +6223,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6241,7 +6232,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6264,48 +6254,51 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133964836</v>
+        <v>133965795</v>
       </c>
       <c r="B52" t="n">
-        <v>91956</v>
+        <v>80485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1108</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>30 maj 26, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590719</v>
+        <v>590416</v>
       </c>
       <c r="R52" t="n">
-        <v>7098092</v>
+        <v>7098273</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6334,7 +6327,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6344,7 +6337,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6353,18 +6346,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
+          <t>David Häggblad, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6375,10 +6369,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133964877</v>
+        <v>133964961</v>
       </c>
       <c r="B53" t="n">
-        <v>91980</v>
+        <v>91956</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6386,19 +6380,23 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6406,10 +6404,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>590454</v>
+        <v>590507</v>
       </c>
       <c r="R53" t="n">
-        <v>7098077</v>
+        <v>7098331</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6441,7 +6439,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6451,7 +6449,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6460,6 +6458,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6482,51 +6481,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133965795</v>
+        <v>133964871</v>
       </c>
       <c r="B54" t="n">
-        <v>80485</v>
+        <v>57972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>30 maj 26, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590416</v>
+        <v>590527</v>
       </c>
       <c r="R54" t="n">
-        <v>7098273</v>
+        <v>7098091</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6555,7 +6551,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6565,7 +6561,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6574,19 +6575,18 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>David Häggblad, Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6713,10 +6713,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133964907</v>
+        <v>133964890</v>
       </c>
       <c r="B56" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6724,21 +6724,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>590374</v>
+        <v>590383</v>
       </c>
       <c r="R56" t="n">
-        <v>7097827</v>
+        <v>7097936</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6824,10 +6824,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133964860</v>
+        <v>133964907</v>
       </c>
       <c r="B57" t="n">
-        <v>91960</v>
+        <v>79359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590597</v>
+        <v>590374</v>
       </c>
       <c r="R57" t="n">
-        <v>7098017</v>
+        <v>7097827</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6935,10 +6935,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133964890</v>
+        <v>133964860</v>
       </c>
       <c r="B58" t="n">
-        <v>80474</v>
+        <v>91960</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6946,21 +6946,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>590383</v>
+        <v>590597</v>
       </c>
       <c r="R58" t="n">
-        <v>7097936</v>
+        <v>7098017</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7273,45 +7273,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133964939</v>
+        <v>133965722</v>
       </c>
       <c r="B61" t="n">
-        <v>80474</v>
+        <v>99203</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Åsele lördag invent., Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>590396</v>
+        <v>590710</v>
       </c>
       <c r="R61" t="n">
-        <v>7098243</v>
+        <v>7098164</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7343,7 +7343,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7368,12 +7368,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj, Christoffer Boman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7384,45 +7384,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133965722</v>
+        <v>133964939</v>
       </c>
       <c r="B62" t="n">
-        <v>99203</v>
+        <v>80474</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Åsele lördag invent., Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>590710</v>
+        <v>590396</v>
       </c>
       <c r="R62" t="n">
-        <v>7098164</v>
+        <v>7098243</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7479,12 +7479,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Katerina Shytaj, Christoffer Boman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7717,32 +7717,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133964908</v>
+        <v>133964839</v>
       </c>
       <c r="B65" t="n">
-        <v>80474</v>
+        <v>96399</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7752,13 +7752,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>590331</v>
+        <v>590716</v>
       </c>
       <c r="R65" t="n">
-        <v>7097828</v>
+        <v>7098081</v>
       </c>
       <c r="S65" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7828,32 +7828,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133964839</v>
+        <v>133964908</v>
       </c>
       <c r="B66" t="n">
-        <v>96399</v>
+        <v>80474</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7863,13 +7863,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>590716</v>
+        <v>590331</v>
       </c>
       <c r="R66" t="n">
-        <v>7098081</v>
+        <v>7097828</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8499,10 +8499,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134034845</v>
+        <v>134034832</v>
       </c>
       <c r="B72" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8510,21 +8510,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8534,13 +8534,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>590286</v>
+        <v>590408</v>
       </c>
       <c r="R72" t="n">
-        <v>7097910</v>
+        <v>7097938</v>
       </c>
       <c r="S72" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8579,12 +8579,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt, med apotecier</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8726,10 +8721,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134034832</v>
+        <v>134034845</v>
       </c>
       <c r="B74" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8737,21 +8732,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8761,13 +8756,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>590408</v>
+        <v>590286</v>
       </c>
       <c r="R74" t="n">
-        <v>7097938</v>
+        <v>7097910</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8796,7 +8791,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8806,7 +8801,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt, med apotecier</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8956,10 +8956,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134034806</v>
+        <v>134034819</v>
       </c>
       <c r="B76" t="n">
-        <v>96399</v>
+        <v>80479</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8967,21 +8967,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>590657</v>
+        <v>590396</v>
       </c>
       <c r="R76" t="n">
-        <v>7098091</v>
+        <v>7097974</v>
       </c>
       <c r="S76" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9067,32 +9067,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134034805</v>
+        <v>134034801</v>
       </c>
       <c r="B77" t="n">
-        <v>89340</v>
+        <v>96399</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>510</v>
+        <v>2809</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9102,13 +9102,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>590688</v>
+        <v>590677</v>
       </c>
       <c r="R77" t="n">
-        <v>7098041</v>
+        <v>7098123</v>
       </c>
       <c r="S77" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9178,32 +9178,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134034819</v>
+        <v>134034805</v>
       </c>
       <c r="B78" t="n">
-        <v>80479</v>
+        <v>89340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>510</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9213,13 +9213,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>590396</v>
+        <v>590688</v>
       </c>
       <c r="R78" t="n">
-        <v>7097974</v>
+        <v>7098041</v>
       </c>
       <c r="S78" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9289,7 +9289,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134034801</v>
+        <v>134034806</v>
       </c>
       <c r="B79" t="n">
         <v>96399</v>
@@ -9324,13 +9324,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>590677</v>
+        <v>590657</v>
       </c>
       <c r="R79" t="n">
-        <v>7098123</v>
+        <v>7098091</v>
       </c>
       <c r="S79" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9845,10 +9845,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134034799</v>
+        <v>134034828</v>
       </c>
       <c r="B84" t="n">
-        <v>99098</v>
+        <v>80485</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219790</v>
+        <v>6463</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9880,13 +9880,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>590702</v>
+        <v>590409</v>
       </c>
       <c r="R84" t="n">
-        <v>7098167</v>
+        <v>7097936</v>
       </c>
       <c r="S84" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9956,10 +9956,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134034828</v>
+        <v>134034831</v>
       </c>
       <c r="B85" t="n">
-        <v>80485</v>
+        <v>80479</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9967,21 +9967,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9991,13 +9991,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>590409</v>
+        <v>590408</v>
       </c>
       <c r="R85" t="n">
-        <v>7097936</v>
+        <v>7097938</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10067,10 +10067,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134034831</v>
+        <v>134034799</v>
       </c>
       <c r="B86" t="n">
-        <v>80479</v>
+        <v>99098</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10078,21 +10078,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10102,13 +10102,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>590408</v>
+        <v>590702</v>
       </c>
       <c r="R86" t="n">
-        <v>7097938</v>
+        <v>7098167</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
+          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -10178,10 +10178,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134034793</v>
+        <v>134034823</v>
       </c>
       <c r="B87" t="n">
-        <v>99203</v>
+        <v>80479</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10189,21 +10189,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10213,13 +10213,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>590704</v>
+        <v>590347</v>
       </c>
       <c r="R87" t="n">
-        <v>7098064</v>
+        <v>7097934</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10243,22 +10243,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10289,10 +10289,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134034823</v>
+        <v>134034793</v>
       </c>
       <c r="B88" t="n">
-        <v>80479</v>
+        <v>99203</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10300,21 +10300,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10324,13 +10324,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>590347</v>
+        <v>590704</v>
       </c>
       <c r="R88" t="n">
-        <v>7097934</v>
+        <v>7098064</v>
       </c>
       <c r="S88" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10354,22 +10354,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
+          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10845,10 +10845,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134034829</v>
+        <v>134034830</v>
       </c>
       <c r="B93" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10856,21 +10856,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10880,13 +10880,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>590409</v>
+        <v>590408</v>
       </c>
       <c r="R93" t="n">
-        <v>7097936</v>
+        <v>7097938</v>
       </c>
       <c r="S93" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10956,10 +10956,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134034830</v>
+        <v>134034829</v>
       </c>
       <c r="B94" t="n">
-        <v>80486</v>
+        <v>80479</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10967,21 +10967,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10991,13 +10991,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>590408</v>
+        <v>590409</v>
       </c>
       <c r="R94" t="n">
-        <v>7097938</v>
+        <v>7097936</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11406,32 +11406,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134034826</v>
+        <v>134034812</v>
       </c>
       <c r="B98" t="n">
-        <v>80486</v>
+        <v>83344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11441,13 +11441,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>590359</v>
+        <v>590583</v>
       </c>
       <c r="R98" t="n">
-        <v>7097903</v>
+        <v>7098061</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11486,12 +11486,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11511,7 +11506,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
+          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11522,32 +11517,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134034812</v>
+        <v>134034794</v>
       </c>
       <c r="B99" t="n">
-        <v>83344</v>
+        <v>99098</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6440</v>
+        <v>219790</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11557,13 +11552,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>590583</v>
+        <v>590727</v>
       </c>
       <c r="R99" t="n">
-        <v>7098061</v>
+        <v>7098083</v>
       </c>
       <c r="S99" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11587,22 +11582,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11749,10 +11744,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134034794</v>
+        <v>134034826</v>
       </c>
       <c r="B101" t="n">
-        <v>99098</v>
+        <v>80486</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11760,21 +11755,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219790</v>
+        <v>6464</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11784,13 +11779,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>590727</v>
+        <v>590359</v>
       </c>
       <c r="R101" t="n">
-        <v>7098083</v>
+        <v>7097903</v>
       </c>
       <c r="S101" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11814,22 +11809,27 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11860,32 +11860,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134034820</v>
+        <v>134034847</v>
       </c>
       <c r="B102" t="n">
-        <v>80474</v>
+        <v>80368</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11895,13 +11895,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>590383</v>
+        <v>590301</v>
       </c>
       <c r="R102" t="n">
-        <v>7097983</v>
+        <v>7098099</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11971,32 +11971,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134034847</v>
+        <v>134034820</v>
       </c>
       <c r="B103" t="n">
-        <v>80368</v>
+        <v>80474</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12006,13 +12006,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>590301</v>
+        <v>590383</v>
       </c>
       <c r="R103" t="n">
-        <v>7098099</v>
+        <v>7097983</v>
       </c>
       <c r="S103" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12193,30 +12193,34 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134034803</v>
+        <v>134034818</v>
       </c>
       <c r="B105" t="n">
-        <v>91980</v>
+        <v>80479</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -12224,13 +12228,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>590716</v>
+        <v>590384</v>
       </c>
       <c r="R105" t="n">
-        <v>7098092</v>
+        <v>7098011</v>
       </c>
       <c r="S105" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12259,7 +12263,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12269,7 +12273,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12300,32 +12304,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134034818</v>
+        <v>134034840</v>
       </c>
       <c r="B106" t="n">
-        <v>80479</v>
+        <v>91956</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12335,13 +12339,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>590384</v>
+        <v>590291</v>
       </c>
       <c r="R106" t="n">
-        <v>7098011</v>
+        <v>7097871</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12370,7 +12374,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12380,7 +12384,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12400,7 +12404,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12411,10 +12415,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134034840</v>
+        <v>134034803</v>
       </c>
       <c r="B107" t="n">
-        <v>91956</v>
+        <v>91980</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12422,23 +12426,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -12446,13 +12446,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>590291</v>
+        <v>590716</v>
       </c>
       <c r="R107" t="n">
-        <v>7097871</v>
+        <v>7098092</v>
       </c>
       <c r="S107" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
+          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">

--- a/artfynd/A 50360-2025 artfynd.xlsx
+++ b/artfynd/A 50360-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133965792</v>
+        <v>133964875</v>
       </c>
       <c r="B2" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>30 maj 26, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590396</v>
+        <v>590484</v>
       </c>
       <c r="R2" t="n">
-        <v>7098248</v>
+        <v>7098087</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133964901</v>
+        <v>133964872</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>80485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590364</v>
+        <v>590498</v>
       </c>
       <c r="R3" t="n">
-        <v>7097857</v>
+        <v>7098099</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,34 +897,30 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133964872</v>
+        <v>133964893</v>
       </c>
       <c r="B4" t="n">
-        <v>80478</v>
+        <v>91987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590498</v>
+        <v>590383</v>
       </c>
       <c r="R4" t="n">
-        <v>7098099</v>
+        <v>7097909</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133964875</v>
+        <v>133964901</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590484</v>
+        <v>590364</v>
       </c>
       <c r="R5" t="n">
-        <v>7098087</v>
+        <v>7097857</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1088,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133964893</v>
+        <v>133965792</v>
       </c>
       <c r="B6" t="n">
-        <v>91980</v>
+        <v>80481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1130,33 +1126,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>30 maj 26, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590383</v>
+        <v>590396</v>
       </c>
       <c r="R6" t="n">
-        <v>7097909</v>
+        <v>7098248</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,12 +1210,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1229,7 +1229,7 @@
         <v>133964878</v>
       </c>
       <c r="B7" t="n">
-        <v>80486</v>
+        <v>80493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133964244</v>
+        <v>133964896</v>
       </c>
       <c r="B8" t="n">
-        <v>80479</v>
+        <v>80493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,34 +1348,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blåkullbäcken, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590649</v>
+        <v>590362</v>
       </c>
       <c r="R8" t="n">
-        <v>7098076</v>
+        <v>7097904</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,12 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På Sälg</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,12 +1432,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1453,7 +1448,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133964896</v>
+        <v>133964244</v>
       </c>
       <c r="B9" t="n">
         <v>80486</v>
@@ -1464,34 +1459,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Blåkullbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590362</v>
+        <v>590649</v>
       </c>
       <c r="R9" t="n">
-        <v>7097904</v>
+        <v>7098076</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,7 +1518,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1528,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På Sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,12 +1548,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1564,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133964919</v>
+        <v>133964967</v>
       </c>
       <c r="B10" t="n">
-        <v>91974</v>
+        <v>91967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590203</v>
+        <v>590510</v>
       </c>
       <c r="R10" t="n">
-        <v>7097878</v>
+        <v>7098266</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,45 +1675,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133965724</v>
+        <v>133964919</v>
       </c>
       <c r="B11" t="n">
-        <v>99203</v>
+        <v>91981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åsele lördag invent., Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590654</v>
+        <v>590203</v>
       </c>
       <c r="R11" t="n">
-        <v>7098070</v>
+        <v>7097878</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,12 +1770,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Katerina Shytaj, Christoffer Boman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1786,45 +1786,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133964967</v>
+        <v>133965724</v>
       </c>
       <c r="B12" t="n">
-        <v>91960</v>
+        <v>99210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Åsele lördag invent., Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590510</v>
+        <v>590654</v>
       </c>
       <c r="R12" t="n">
-        <v>7098266</v>
+        <v>7098070</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,12 +1881,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj, Christoffer Boman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1897,48 +1897,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133965790</v>
+        <v>133964924</v>
       </c>
       <c r="B13" t="n">
-        <v>80479</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>30 maj 26, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590412</v>
+        <v>590257</v>
       </c>
       <c r="R13" t="n">
-        <v>7098210</v>
+        <v>7097936</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,12 +1992,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2011,7 +2011,7 @@
         <v>133964911</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,48 +2119,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133964924</v>
+        <v>133965790</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>80486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>30 maj 26, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590257</v>
+        <v>590412</v>
       </c>
       <c r="R15" t="n">
-        <v>7097936</v>
+        <v>7098210</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2214,12 +2214,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2230,10 +2230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133964951</v>
+        <v>133964243</v>
       </c>
       <c r="B16" t="n">
-        <v>83349</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2241,37 +2241,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Blåkullbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590464</v>
+        <v>590710</v>
       </c>
       <c r="R16" t="n">
-        <v>7098263</v>
+        <v>7098212</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2310,7 +2310,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Pa granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,12 +2330,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2341,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133964894</v>
+        <v>133964854</v>
       </c>
       <c r="B17" t="n">
-        <v>80474</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2352,21 +2357,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2376,10 +2381,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590364</v>
+        <v>590630</v>
       </c>
       <c r="R17" t="n">
-        <v>7097903</v>
+        <v>7098063</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2411,7 +2416,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2421,7 +2426,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,7 +2440,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2456,7 +2465,7 @@
         <v>133964835</v>
       </c>
       <c r="B18" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2564,10 +2573,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133964854</v>
+        <v>133964894</v>
       </c>
       <c r="B19" t="n">
-        <v>57972</v>
+        <v>80481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2575,21 +2584,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2599,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590630</v>
+        <v>590364</v>
       </c>
       <c r="R19" t="n">
-        <v>7098063</v>
+        <v>7097903</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2634,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2644,12 +2653,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,6 +2662,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2680,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133964243</v>
+        <v>133964951</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>83356</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2691,37 +2696,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blåkullbäcken, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>590710</v>
+        <v>590464</v>
       </c>
       <c r="R20" t="n">
-        <v>7098212</v>
+        <v>7098263</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2750,7 +2755,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2760,12 +2765,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Pa granlåga</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,12 +2780,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2796,10 +2796,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133965791</v>
+        <v>133964898</v>
       </c>
       <c r="B21" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,17 +2827,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>30 maj 26, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>590412</v>
+        <v>590367</v>
       </c>
       <c r="R21" t="n">
-        <v>7098210</v>
+        <v>7097883</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,12 +2891,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2907,32 +2907,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133964932</v>
+        <v>133964865</v>
       </c>
       <c r="B22" t="n">
-        <v>80368</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2942,10 +2942,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>590409</v>
+        <v>590567</v>
       </c>
       <c r="R22" t="n">
-        <v>7098210</v>
+        <v>7098043</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3018,32 +3018,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133964865</v>
+        <v>133964932</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>80375</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>590567</v>
+        <v>590409</v>
       </c>
       <c r="R23" t="n">
-        <v>7098043</v>
+        <v>7098210</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3129,10 +3129,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133964898</v>
+        <v>133964882</v>
       </c>
       <c r="B24" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,21 +3140,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>590367</v>
+        <v>590358</v>
       </c>
       <c r="R24" t="n">
-        <v>7097883</v>
+        <v>7098027</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,45 +3240,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133964882</v>
+        <v>133964242</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>99210</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Blåkullbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>590358</v>
+        <v>590710</v>
       </c>
       <c r="R25" t="n">
-        <v>7098027</v>
+        <v>7098212</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3320,7 +3320,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Granskog på vitmossa</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,12 +3340,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3351,48 +3356,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133964242</v>
+        <v>133965791</v>
       </c>
       <c r="B26" t="n">
-        <v>99203</v>
+        <v>80481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blåkullbäcken, Ås lm</t>
+          <t>30 maj 26, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>590710</v>
+        <v>590412</v>
       </c>
       <c r="R26" t="n">
-        <v>7098212</v>
+        <v>7098210</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3421,7 +3426,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3431,12 +3436,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Granskog på vitmossa</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3451,12 +3451,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3470,7 +3470,7 @@
         <v>133964863</v>
       </c>
       <c r="B27" t="n">
-        <v>83336</v>
+        <v>83343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3579,32 +3579,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133964868</v>
+        <v>133964829</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>99210</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3614,10 +3614,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>590559</v>
+        <v>590712</v>
       </c>
       <c r="R28" t="n">
-        <v>7098066</v>
+        <v>7098203</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3690,32 +3690,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133964833</v>
+        <v>133964943</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>80493</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>590703</v>
+        <v>590396</v>
       </c>
       <c r="R29" t="n">
-        <v>7098166</v>
+        <v>7098245</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3801,32 +3801,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133964943</v>
+        <v>133964833</v>
       </c>
       <c r="B30" t="n">
-        <v>80486</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>590396</v>
+        <v>590703</v>
       </c>
       <c r="R30" t="n">
-        <v>7098245</v>
+        <v>7098166</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3912,32 +3912,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133964829</v>
+        <v>133964868</v>
       </c>
       <c r="B31" t="n">
-        <v>99203</v>
+        <v>79366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>590712</v>
+        <v>590559</v>
       </c>
       <c r="R31" t="n">
-        <v>7098203</v>
+        <v>7098066</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4023,48 +4023,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133964704</v>
+        <v>133964931</v>
       </c>
       <c r="B32" t="n">
-        <v>99203</v>
+        <v>91967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lördag, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>590716</v>
+        <v>590360</v>
       </c>
       <c r="R32" t="n">
-        <v>7098211</v>
+        <v>7098115</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4118,12 +4118,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sara Ranesson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sara Ranesson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -4134,10 +4134,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133964887</v>
+        <v>133964704</v>
       </c>
       <c r="B33" t="n">
-        <v>80486</v>
+        <v>99210</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4145,37 +4145,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Lördag, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>590374</v>
+        <v>590716</v>
       </c>
       <c r="R33" t="n">
-        <v>7097948</v>
+        <v>7098211</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4229,12 +4229,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sara Ranesson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Sara Ranesson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4245,32 +4245,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133964931</v>
+        <v>133964887</v>
       </c>
       <c r="B34" t="n">
-        <v>91960</v>
+        <v>80493</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>590360</v>
+        <v>590374</v>
       </c>
       <c r="R34" t="n">
-        <v>7098115</v>
+        <v>7097948</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4359,7 +4359,7 @@
         <v>133964956</v>
       </c>
       <c r="B35" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4467,10 +4467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133964245</v>
+        <v>133964844</v>
       </c>
       <c r="B36" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4498,17 +4498,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Blåkullbäcken, Ås lm</t>
+          <t>Lördag, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>590419</v>
+        <v>590408</v>
       </c>
       <c r="R36" t="n">
-        <v>7098217</v>
+        <v>7098280</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4547,12 +4547,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4567,12 +4562,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Sara Ranesson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patrik Eriksson</t>
+          <t>Sara Ranesson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4583,10 +4578,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133964844</v>
+        <v>133964245</v>
       </c>
       <c r="B37" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4614,17 +4609,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lördag, Ås lm</t>
+          <t>Blåkullbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>590408</v>
+        <v>590419</v>
       </c>
       <c r="R37" t="n">
-        <v>7098280</v>
+        <v>7098217</v>
       </c>
       <c r="S37" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4653,7 +4648,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4663,7 +4658,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4678,12 +4678,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sara Ranesson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sara Ranesson</t>
+          <t>Patrik Eriksson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4697,7 +4697,7 @@
         <v>133964845</v>
       </c>
       <c r="B38" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133964880</v>
+        <v>133964915</v>
       </c>
       <c r="B39" t="n">
-        <v>96399</v>
+        <v>96406</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>590370</v>
+        <v>590241</v>
       </c>
       <c r="R39" t="n">
-        <v>7098043</v>
+        <v>7097878</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4916,10 +4916,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133964915</v>
+        <v>133964880</v>
       </c>
       <c r="B40" t="n">
-        <v>96399</v>
+        <v>96406</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>590241</v>
+        <v>590370</v>
       </c>
       <c r="R40" t="n">
-        <v>7097878</v>
+        <v>7098043</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5027,10 +5027,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133964927</v>
+        <v>133964960</v>
       </c>
       <c r="B41" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>590366</v>
+        <v>590501</v>
       </c>
       <c r="R41" t="n">
-        <v>7097993</v>
+        <v>7098263</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5141,7 +5141,7 @@
         <v>133964858</v>
       </c>
       <c r="B42" t="n">
-        <v>96399</v>
+        <v>96406</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133964960</v>
+        <v>133964869</v>
       </c>
       <c r="B43" t="n">
-        <v>80474</v>
+        <v>83215</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5260,21 +5260,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>590501</v>
+        <v>590555</v>
       </c>
       <c r="R43" t="n">
-        <v>7098263</v>
+        <v>7098084</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5338,6 +5338,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5360,32 +5361,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133964929</v>
+        <v>133964927</v>
       </c>
       <c r="B44" t="n">
-        <v>80424</v>
+        <v>80481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5471,10 +5472,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133965725</v>
+        <v>133964929</v>
       </c>
       <c r="B45" t="n">
-        <v>80478</v>
+        <v>80431</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5482,34 +5483,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6461</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Åsele lördag invent., Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>590626</v>
+        <v>590366</v>
       </c>
       <c r="R45" t="n">
-        <v>7098051</v>
+        <v>7097993</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5541,7 +5542,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5551,7 +5552,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5566,12 +5567,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Katerina Shytaj</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Katerina Shytaj, Christoffer Boman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5582,45 +5583,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133964869</v>
+        <v>133965723</v>
       </c>
       <c r="B46" t="n">
-        <v>83208</v>
+        <v>99210</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Åsele lördag invent., Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>590555</v>
+        <v>590706</v>
       </c>
       <c r="R46" t="n">
-        <v>7098084</v>
+        <v>7098126</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5652,7 +5653,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5662,7 +5663,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5671,19 +5672,18 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Katerina Shytaj, Christoffer Boman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5694,10 +5694,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133965723</v>
+        <v>133965725</v>
       </c>
       <c r="B47" t="n">
-        <v>99203</v>
+        <v>80485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5705,21 +5705,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221952</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>590706</v>
+        <v>590626</v>
       </c>
       <c r="R47" t="n">
-        <v>7098126</v>
+        <v>7098051</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5808,7 +5808,7 @@
         <v>133965794</v>
       </c>
       <c r="B48" t="n">
-        <v>80479</v>
+        <v>80486</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5925,10 +5925,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133964877</v>
+        <v>133964836</v>
       </c>
       <c r="B49" t="n">
-        <v>91980</v>
+        <v>91963</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5936,19 +5936,23 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -5956,10 +5960,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>590454</v>
+        <v>590719</v>
       </c>
       <c r="R49" t="n">
-        <v>7098077</v>
+        <v>7098092</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5991,7 +5995,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6001,7 +6005,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6021,7 +6025,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6032,10 +6036,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133964836</v>
+        <v>133964871</v>
       </c>
       <c r="B50" t="n">
-        <v>91956</v>
+        <v>57972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6043,21 +6047,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6067,10 +6071,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>590719</v>
+        <v>590527</v>
       </c>
       <c r="R50" t="n">
-        <v>7098092</v>
+        <v>7098091</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6102,7 +6106,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6112,7 +6116,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6132,7 +6141,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6143,34 +6152,30 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133964930</v>
+        <v>133964877</v>
       </c>
       <c r="B51" t="n">
-        <v>99203</v>
+        <v>91987</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6178,10 +6183,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>590389</v>
+        <v>590454</v>
       </c>
       <c r="R51" t="n">
-        <v>7098071</v>
+        <v>7098077</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6213,7 +6218,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6223,7 +6228,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6254,51 +6259,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133965795</v>
+        <v>133964961</v>
       </c>
       <c r="B52" t="n">
-        <v>80485</v>
+        <v>91963</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>30 maj 26, Ås lm</t>
+          <t>Kojmyrriset, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>590416</v>
+        <v>590507</v>
       </c>
       <c r="R52" t="n">
-        <v>7098273</v>
+        <v>7098331</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6327,7 +6329,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6337,7 +6339,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6353,12 +6355,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>David Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>David Häggblad, Karin Häggblad</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6369,32 +6371,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133964961</v>
+        <v>133964930</v>
       </c>
       <c r="B53" t="n">
-        <v>91956</v>
+        <v>99210</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6404,10 +6406,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>590507</v>
+        <v>590389</v>
       </c>
       <c r="R53" t="n">
-        <v>7098331</v>
+        <v>7098071</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6439,7 +6441,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6449,7 +6451,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6458,7 +6460,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6481,10 +6482,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133964871</v>
+        <v>133965942</v>
       </c>
       <c r="B54" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6492,16 +6493,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6512,14 +6513,14 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kojmyrriset, Ås lm</t>
+          <t>Kojmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>590527</v>
+        <v>590496</v>
       </c>
       <c r="R54" t="n">
-        <v>7098091</v>
+        <v>7098343</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6551,7 +6552,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6561,12 +6562,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6581,12 +6582,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Gunnar Janson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Gunnar Janson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6597,48 +6598,51 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133965942</v>
+        <v>133965795</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>80492</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kojmyran, Ås lm</t>
+          <t>30 maj 26, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>590496</v>
+        <v>590416</v>
       </c>
       <c r="R55" t="n">
-        <v>7098343</v>
+        <v>7098273</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6667,7 +6671,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6677,12 +6681,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6691,18 +6690,19 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Gunnar Janson</t>
+          <t>David Häggblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Gunnar Janson</t>
+          <t>David Häggblad, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6713,10 +6713,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133964890</v>
+        <v>133964907</v>
       </c>
       <c r="B56" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6724,21 +6724,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>590383</v>
+        <v>590374</v>
       </c>
       <c r="R56" t="n">
-        <v>7097936</v>
+        <v>7097827</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6824,10 +6824,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133964907</v>
+        <v>133964860</v>
       </c>
       <c r="B57" t="n">
-        <v>79359</v>
+        <v>91967</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6835,21 +6835,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6859,10 +6859,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>590374</v>
+        <v>590597</v>
       </c>
       <c r="R57" t="n">
-        <v>7097827</v>
+        <v>7098017</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6935,32 +6935,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133964860</v>
+        <v>133964862</v>
       </c>
       <c r="B58" t="n">
-        <v>91960</v>
+        <v>83334</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6970,13 +6970,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>590597</v>
+        <v>590591</v>
       </c>
       <c r="R58" t="n">
-        <v>7098017</v>
+        <v>7098042</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7046,32 +7046,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133964862</v>
+        <v>133964890</v>
       </c>
       <c r="B59" t="n">
-        <v>83327</v>
+        <v>80481</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7081,13 +7081,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>590591</v>
+        <v>590383</v>
       </c>
       <c r="R59" t="n">
-        <v>7098042</v>
+        <v>7097936</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7160,7 +7160,7 @@
         <v>133965793</v>
       </c>
       <c r="B60" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>133965722</v>
       </c>
       <c r="B61" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>133964939</v>
       </c>
       <c r="B62" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>133964947</v>
       </c>
       <c r="B63" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>133964884</v>
       </c>
       <c r="B64" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7717,32 +7717,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133964839</v>
+        <v>133964908</v>
       </c>
       <c r="B65" t="n">
-        <v>96399</v>
+        <v>80481</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7752,13 +7752,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>590716</v>
+        <v>590331</v>
       </c>
       <c r="R65" t="n">
-        <v>7098081</v>
+        <v>7097828</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7828,32 +7828,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133964908</v>
+        <v>133964839</v>
       </c>
       <c r="B66" t="n">
-        <v>80474</v>
+        <v>96406</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>2809</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7863,13 +7863,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>590331</v>
+        <v>590716</v>
       </c>
       <c r="R66" t="n">
-        <v>7097828</v>
+        <v>7098081</v>
       </c>
       <c r="S66" t="n">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7942,7 +7942,7 @@
         <v>134004091</v>
       </c>
       <c r="B67" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>134004085</v>
       </c>
       <c r="B68" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>134004088</v>
       </c>
       <c r="B70" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>134004086</v>
       </c>
       <c r="B71" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8499,10 +8499,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134034832</v>
+        <v>134034822</v>
       </c>
       <c r="B72" t="n">
-        <v>80474</v>
+        <v>89347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8510,21 +8510,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8534,13 +8534,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>590408</v>
+        <v>590350</v>
       </c>
       <c r="R72" t="n">
-        <v>7097938</v>
+        <v>7097932</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8610,10 +8610,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134034822</v>
+        <v>134034845</v>
       </c>
       <c r="B73" t="n">
-        <v>89340</v>
+        <v>79366</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8621,21 +8621,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8645,13 +8645,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>590350</v>
+        <v>590286</v>
       </c>
       <c r="R73" t="n">
-        <v>7097932</v>
+        <v>7097910</v>
       </c>
       <c r="S73" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8690,7 +8690,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt, med apotecier</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8721,10 +8726,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134034845</v>
+        <v>134034832</v>
       </c>
       <c r="B74" t="n">
-        <v>79359</v>
+        <v>80481</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8732,21 +8737,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8756,13 +8761,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>590286</v>
+        <v>590408</v>
       </c>
       <c r="R74" t="n">
-        <v>7097910</v>
+        <v>7097938</v>
       </c>
       <c r="S74" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8791,7 +8796,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8801,12 +8806,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt, med apotecier</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8956,10 +8956,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134034819</v>
+        <v>134034806</v>
       </c>
       <c r="B76" t="n">
-        <v>80479</v>
+        <v>96406</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8967,21 +8967,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>590396</v>
+        <v>590657</v>
       </c>
       <c r="R76" t="n">
-        <v>7097974</v>
+        <v>7098091</v>
       </c>
       <c r="S76" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9067,32 +9067,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134034801</v>
+        <v>134034805</v>
       </c>
       <c r="B77" t="n">
-        <v>96399</v>
+        <v>89347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2809</v>
+        <v>510</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9102,13 +9102,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>590677</v>
+        <v>590688</v>
       </c>
       <c r="R77" t="n">
-        <v>7098123</v>
+        <v>7098041</v>
       </c>
       <c r="S77" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9178,32 +9178,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134034805</v>
+        <v>134034801</v>
       </c>
       <c r="B78" t="n">
-        <v>89340</v>
+        <v>96406</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>510</v>
+        <v>2809</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9213,13 +9213,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>590688</v>
+        <v>590677</v>
       </c>
       <c r="R78" t="n">
-        <v>7098041</v>
+        <v>7098123</v>
       </c>
       <c r="S78" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9289,10 +9289,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134034806</v>
+        <v>134034819</v>
       </c>
       <c r="B79" t="n">
-        <v>96399</v>
+        <v>80486</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9300,21 +9300,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2809</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9324,13 +9324,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>590657</v>
+        <v>590396</v>
       </c>
       <c r="R79" t="n">
-        <v>7098091</v>
+        <v>7097974</v>
       </c>
       <c r="S79" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9369,7 +9369,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9403,7 +9403,7 @@
         <v>134034804</v>
       </c>
       <c r="B80" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>134034815</v>
       </c>
       <c r="B81" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>134034849</v>
       </c>
       <c r="B82" t="n">
-        <v>80399</v>
+        <v>80406</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134034814</v>
+        <v>134034831</v>
       </c>
       <c r="B83" t="n">
-        <v>91923</v>
+        <v>80486</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9745,21 +9745,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9769,13 +9769,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>590483</v>
+        <v>590408</v>
       </c>
       <c r="R83" t="n">
-        <v>7098127</v>
+        <v>7097938</v>
       </c>
       <c r="S83" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9845,10 +9845,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134034828</v>
+        <v>134034814</v>
       </c>
       <c r="B84" t="n">
-        <v>80485</v>
+        <v>91930</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9856,21 +9856,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9880,13 +9880,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>590409</v>
+        <v>590483</v>
       </c>
       <c r="R84" t="n">
-        <v>7097936</v>
+        <v>7098127</v>
       </c>
       <c r="S84" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
+          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9956,10 +9956,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134034831</v>
+        <v>134034828</v>
       </c>
       <c r="B85" t="n">
-        <v>80479</v>
+        <v>80492</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9967,21 +9967,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9991,13 +9991,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>590408</v>
+        <v>590409</v>
       </c>
       <c r="R85" t="n">
-        <v>7097938</v>
+        <v>7097936</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10070,7 +10070,7 @@
         <v>134034799</v>
       </c>
       <c r="B86" t="n">
-        <v>99098</v>
+        <v>99105</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10178,10 +10178,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134034823</v>
+        <v>134034793</v>
       </c>
       <c r="B87" t="n">
-        <v>80479</v>
+        <v>99210</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10189,21 +10189,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10213,13 +10213,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>590347</v>
+        <v>590704</v>
       </c>
       <c r="R87" t="n">
-        <v>7097934</v>
+        <v>7098064</v>
       </c>
       <c r="S87" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10243,22 +10243,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
+          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10289,10 +10289,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134034793</v>
+        <v>134034823</v>
       </c>
       <c r="B88" t="n">
-        <v>99203</v>
+        <v>80486</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10300,21 +10300,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10324,13 +10324,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>590704</v>
+        <v>590347</v>
       </c>
       <c r="R88" t="n">
-        <v>7098064</v>
+        <v>7097934</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10354,22 +10354,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -10403,7 +10403,7 @@
         <v>134034792</v>
       </c>
       <c r="B89" t="n">
-        <v>89340</v>
+        <v>89347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>134034836</v>
       </c>
       <c r="B90" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>134034791</v>
       </c>
       <c r="B91" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>134034846</v>
       </c>
       <c r="B92" t="n">
-        <v>80368</v>
+        <v>80375</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134034830</v>
+        <v>134034829</v>
       </c>
       <c r="B93" t="n">
         <v>80486</v>
@@ -10856,21 +10856,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10880,13 +10880,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>590408</v>
+        <v>590409</v>
       </c>
       <c r="R93" t="n">
-        <v>7097938</v>
+        <v>7097936</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10956,10 +10956,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134034829</v>
+        <v>134034830</v>
       </c>
       <c r="B94" t="n">
-        <v>80479</v>
+        <v>80493</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10967,21 +10967,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10991,13 +10991,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>590409</v>
+        <v>590408</v>
       </c>
       <c r="R94" t="n">
-        <v>7097936</v>
+        <v>7097938</v>
       </c>
       <c r="S94" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11186,7 +11186,7 @@
         <v>134034809</v>
       </c>
       <c r="B96" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11295,10 +11295,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134034790</v>
+        <v>134034826</v>
       </c>
       <c r="B97" t="n">
-        <v>96399</v>
+        <v>80493</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11306,21 +11306,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11330,13 +11330,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>590706</v>
+        <v>590359</v>
       </c>
       <c r="R97" t="n">
-        <v>7098092</v>
+        <v>7097903</v>
       </c>
       <c r="S97" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11360,22 +11360,27 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11395,7 +11400,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11406,10 +11411,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134034812</v>
+        <v>134034789</v>
       </c>
       <c r="B98" t="n">
-        <v>83344</v>
+        <v>57975</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11417,37 +11422,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Kojmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>590583</v>
+        <v>590693</v>
       </c>
       <c r="R98" t="n">
-        <v>7098061</v>
+        <v>7098112</v>
       </c>
       <c r="S98" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11471,22 +11481,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11506,7 +11516,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11517,10 +11527,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134034794</v>
+        <v>134034790</v>
       </c>
       <c r="B99" t="n">
-        <v>99098</v>
+        <v>96406</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11528,21 +11538,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219790</v>
+        <v>2809</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11552,13 +11562,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>590727</v>
+        <v>590706</v>
       </c>
       <c r="R99" t="n">
-        <v>7098083</v>
+        <v>7098092</v>
       </c>
       <c r="S99" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11587,7 +11597,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11597,7 +11607,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11617,7 +11627,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11628,10 +11638,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134034789</v>
+        <v>134034812</v>
       </c>
       <c r="B100" t="n">
-        <v>57975</v>
+        <v>83351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11639,42 +11649,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kojmyran, Ås lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>590693</v>
+        <v>590583</v>
       </c>
       <c r="R100" t="n">
-        <v>7098112</v>
+        <v>7098061</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11698,22 +11703,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11733,7 +11738,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11744,10 +11749,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134034826</v>
+        <v>134034794</v>
       </c>
       <c r="B101" t="n">
-        <v>80486</v>
+        <v>99105</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11755,21 +11760,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>219790</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11779,13 +11784,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>590359</v>
+        <v>590727</v>
       </c>
       <c r="R101" t="n">
-        <v>7097903</v>
+        <v>7098083</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11809,27 +11814,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
+          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -11860,32 +11860,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134034847</v>
+        <v>134034820</v>
       </c>
       <c r="B102" t="n">
-        <v>80368</v>
+        <v>80481</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11895,13 +11895,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>590301</v>
+        <v>590383</v>
       </c>
       <c r="R102" t="n">
-        <v>7098099</v>
+        <v>7097983</v>
       </c>
       <c r="S102" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11971,32 +11971,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134034820</v>
+        <v>134034847</v>
       </c>
       <c r="B103" t="n">
-        <v>80474</v>
+        <v>80375</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12006,13 +12006,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>590383</v>
+        <v>590301</v>
       </c>
       <c r="R103" t="n">
-        <v>7097983</v>
+        <v>7098099</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12085,7 +12085,7 @@
         <v>134034817</v>
       </c>
       <c r="B104" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12193,32 +12193,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134034818</v>
+        <v>134034840</v>
       </c>
       <c r="B105" t="n">
-        <v>80479</v>
+        <v>91963</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12228,13 +12228,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>590384</v>
+        <v>590291</v>
       </c>
       <c r="R105" t="n">
-        <v>7098011</v>
+        <v>7097871</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
+          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -12304,10 +12304,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134034840</v>
+        <v>134034803</v>
       </c>
       <c r="B106" t="n">
-        <v>91956</v>
+        <v>91987</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12315,23 +12315,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -12339,13 +12335,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>590291</v>
+        <v>590716</v>
       </c>
       <c r="R106" t="n">
-        <v>7097871</v>
+        <v>7098092</v>
       </c>
       <c r="S106" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12374,7 +12370,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12384,7 +12380,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12404,7 +12400,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Anton Brall, Katerina Shytaj, Gunnar Janson</t>
+          <t>Elin Kannerby, Alva Danielsson, Gunnar Janson, Anton Brall, Sture Gustafsson, David Häggblad, Karin Häggblad, Patrik Eriksson, Katerina Shytaj</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12415,30 +12411,34 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134034803</v>
+        <v>134034818</v>
       </c>
       <c r="B107" t="n">
-        <v>91980</v>
+        <v>80486</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -12446,13 +12446,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>590716</v>
+        <v>590384</v>
       </c>
       <c r="R107" t="n">
-        <v>7098092</v>
+        <v>7098011</v>
       </c>
       <c r="S107" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12522,32 +12522,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134034824</v>
+        <v>134034825</v>
       </c>
       <c r="B108" t="n">
-        <v>80486</v>
+        <v>80481</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12557,13 +12557,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>590349</v>
+        <v>590361</v>
       </c>
       <c r="R108" t="n">
-        <v>7097931</v>
+        <v>7097902</v>
       </c>
       <c r="S108" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12602,7 +12602,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12633,32 +12638,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134034825</v>
+        <v>134034824</v>
       </c>
       <c r="B109" t="n">
-        <v>80474</v>
+        <v>80493</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12668,13 +12673,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>590361</v>
+        <v>590349</v>
       </c>
       <c r="R109" t="n">
-        <v>7097902</v>
+        <v>7097931</v>
       </c>
       <c r="S109" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12703,7 +12708,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12713,12 +12718,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD109" t="b">

--- a/artfynd/A 50360-2025 artfynd.xlsx
+++ b/artfynd/A 50360-2025 artfynd.xlsx
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
+          <t>Alva Danielsson, Karin Häggblad, Sture Gustafsson, David Häggblad, Patrik Eriksson, Sara Ranesson, Katerina Shytaj, Gunnar Andersson, Maria Persbo, Anton Brall, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
+          <t>Alva Danielsson, Karin Häggblad, Sture Gustafsson, David Häggblad, Patrik Eriksson, Sara Ranesson, Katerina Shytaj, Gunnar Andersson, Maria Persbo, Anton Brall, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
+          <t>Alva Danielsson, Karin Häggblad, Sture Gustafsson, David Häggblad, Patrik Eriksson, Sara Ranesson, Katerina Shytaj, Gunnar Andersson, Maria Persbo, Anton Brall, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
+          <t>Alva Danielsson, Karin Häggblad, Sture Gustafsson, David Häggblad, Patrik Eriksson, Sara Ranesson, Katerina Shytaj, Gunnar Andersson, Maria Persbo, Anton Brall, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
+          <t>Alva Danielsson, Karin Häggblad, Sture Gustafsson, David Häggblad, Patrik Eriksson, Sara Ranesson, Katerina Shytaj, Gunnar Andersson, Maria Persbo, Anton Brall, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">

--- a/artfynd/A 50360-2025 artfynd.xlsx
+++ b/artfynd/A 50360-2025 artfynd.xlsx
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Karin Häggblad, Sture Gustafsson, David Häggblad, Patrik Eriksson, Sara Ranesson, Katerina Shytaj, Gunnar Andersson, Maria Persbo, Anton Brall, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Karin Häggblad, Sture Gustafsson, David Häggblad, Patrik Eriksson, Sara Ranesson, Katerina Shytaj, Gunnar Andersson, Maria Persbo, Anton Brall, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Karin Häggblad, Sture Gustafsson, David Häggblad, Patrik Eriksson, Sara Ranesson, Katerina Shytaj, Gunnar Andersson, Maria Persbo, Anton Brall, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Karin Häggblad, Sture Gustafsson, David Häggblad, Patrik Eriksson, Sara Ranesson, Katerina Shytaj, Gunnar Andersson, Maria Persbo, Anton Brall, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Karin Häggblad, Sture Gustafsson, David Häggblad, Patrik Eriksson, Sara Ranesson, Katerina Shytaj, Gunnar Andersson, Maria Persbo, Anton Brall, Elin Kannerby</t>
+          <t>Alva Danielsson, Elin Kannerby, Anton Brall, Maria Persbo, Gunnar Andersson, Katerina Shytaj, Sara Ranesson, Patrik Eriksson, David Häggblad, Sture Gustafsson, Karin Häggblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">

--- a/artfynd/A 50360-2025 artfynd.xlsx
+++ b/artfynd/A 50360-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY115"/>
+  <dimension ref="A1:AZ115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964863</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034792</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034805</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034822</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964836</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964956</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964961</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034840</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1674,6 +1719,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964860</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964931</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1896,6 +1951,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964967</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2007,6 +2067,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034817</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2118,6 +2183,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964919</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2230,6 +2300,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964869</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2342,6 +2417,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034809</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2453,6 +2533,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964951</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2564,6 +2649,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964839</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2675,6 +2765,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964858</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2786,6 +2881,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964880</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2897,6 +2997,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964915</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3008,6 +3113,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034790</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3119,6 +3229,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034801</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3230,6 +3345,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034806</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3341,6 +3461,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964849</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3452,6 +3577,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964845</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3563,6 +3693,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034814</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3679,6 +3814,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964243</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3790,6 +3930,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964833</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3901,6 +4046,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964865</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4012,6 +4162,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964868</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4123,6 +4278,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964875</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4234,6 +4394,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964882</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4345,6 +4510,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964901</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4456,6 +4626,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964907</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4567,6 +4742,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964911</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4678,6 +4858,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964924</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4789,6 +4974,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964947</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4900,6 +5090,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134004085</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5011,6 +5206,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134004086</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5122,6 +5322,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134004088</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5233,6 +5438,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134004091</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5349,6 +5559,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034804</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5465,6 +5680,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034845</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5576,6 +5796,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964862</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5687,6 +5912,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034812</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5798,6 +6028,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964932</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5909,6 +6144,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034846</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6020,6 +6260,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034847</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6131,6 +6376,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034849</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6247,6 +6497,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964245</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6358,6 +6613,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964710</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6469,6 +6729,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964890</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6581,6 +6846,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964894</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6692,6 +6962,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964898</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6803,6 +7078,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964927</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6914,6 +7194,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964939</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7025,6 +7310,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964960</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7136,6 +7426,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965791</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7247,6 +7542,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965792</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7363,6 +7663,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965793</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7474,6 +7779,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034820</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7590,6 +7900,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034825</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7701,6 +8016,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034832</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7812,6 +8132,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034836</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7923,6 +8248,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964872</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8034,6 +8364,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965725</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8145,6 +8480,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034795</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8261,6 +8601,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964244</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8370,6 +8715,11 @@
       <c r="AY70" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965790</t>
         </is>
       </c>
     </row>
@@ -8492,6 +8842,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965794</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8603,6 +8958,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034818</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8714,6 +9074,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034819</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8825,6 +9190,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034823</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8936,6 +9306,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034829</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9045,6 +9420,11 @@
       <c r="AY76" t="inlineStr">
         <is>
           <t>Inventeringshelg Åsele maj 2026</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034831</t>
         </is>
       </c>
     </row>
@@ -9162,6 +9542,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965795</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9273,6 +9658,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034828</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9384,6 +9774,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964878</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9495,6 +9890,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964887</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9606,6 +10006,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964896</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9717,6 +10122,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964943</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9828,6 +10238,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034824</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9944,6 +10359,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034826</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10055,6 +10475,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034830</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10171,6 +10596,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964854</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10287,6 +10717,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964871</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10398,6 +10833,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034833</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10514,6 +10954,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965942</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10630,6 +11075,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134004092</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10746,6 +11196,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034789</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10865,6 +11320,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034842</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10981,6 +11441,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034843</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11097,6 +11562,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034844</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11208,6 +11678,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034794</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11319,6 +11794,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034799</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11430,6 +11910,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964831</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11541,6 +12026,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964852</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11652,6 +12142,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964935</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11763,6 +12258,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034800</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11879,6 +12379,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964242</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11990,6 +12495,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964704</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12101,6 +12611,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964829</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12212,6 +12727,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964835</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12323,6 +12843,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964884</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12434,6 +12959,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964930</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12545,6 +13075,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965721</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12656,6 +13191,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965723</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12767,6 +13307,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965724</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12878,6 +13423,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034791</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12989,6 +13539,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034793</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13100,6 +13655,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034808</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13216,6 +13776,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965727</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13328,6 +13893,11 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134034807</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13439,8 +14009,129 @@
           <t>Inventeringshelg Åsele maj 2026</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964929</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>